--- a/stories/arbres/ATOM-JEU.FOOT.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dounia et maman arrivent au jardin. L'herbe sent l'été. Maman pose deux gourdes. Elle trace un petit rectangle. Maman dit : voici l'espace montré. On reste dans l'espace montré. Au fond, maman pose deux paniers. C'est le but. Dounia touche le ballon du pied. Le ballon est souple. Maman dit : on va passer le ballon. Puis on vise le but. Dounia passe le ballon à maman. Maman le rend. Dounia pousse le ballon vers le but. Le ballon roule entre les paniers. Dounia lève les bras. Maman dit : on reste dans le rectangle. Dounia ramène le ballon. Elle passe encore. Elle vise encore le but. Les pieds restent dans l'espace montré par maman.</t>
+          <t>Dounia et maman arrivent au jardin. L'herbe sent l'été. Maman pose deux gourdes. Elle trace un petit rectangle. Voici l'espace montré. On reste dans l'espace montré. Au fond, maman pose deux paniers. C'est le but. Dounia touche le ballon du pied. Le ballon est souple. On va passer le ballon. Puis on vise le but. Dounia passe le ballon à maman. Maman le rend. Dounia pousse le ballon vers le but. Le ballon roule entre les paniers. Dounia lève les bras. On reste dans le rectangle. Dounia ramène le ballon. Elle passe encore. Elle vise encore le but. Les pieds restent dans l'espace montré par maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Dounia et maman arrivent au jardin. L'herbe sent l'été. Maman pose deux gourdes. Elle trace un petit rectangle.
+maman|Voici l'espace montré. On reste dans l'espace montré. Au fond, maman pose deux paniers. C'est le but.
+narrateur|Dounia touche le ballon du pied. Le ballon est souple.
+maman|On va passer le ballon.
+narrateur|Puis on vise le but. Dounia passe le ballon à maman. Maman le rend. Dounia pousse le ballon vers le but. Le ballon roule entre les paniers. Dounia lève les bras.
+maman|On reste dans le rectangle.
+narrateur|Dounia ramène le ballon. Elle passe encore. Elle vise encore le but. Les pieds restent dans l'espace montré par maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Dounia joue au foot. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dounia a passé le ballon. Elle a visé le but. Elle est restée dans l'espace montré par maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range les paniers. Dounia boit une gorgée. Elles marchent vers la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.FOOT.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Dounia ramène le ballon. Elle passe encore. Elle vise encore le but. Les pieds restent dans l'espace montré par maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Dounia joue au foot. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Dounia a passé le ballon. Elle a visé le but. Elle est restée dans l'espace montré par maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Maman range les paniers. Dounia boit une gorgée. Elles marchent vers la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.FOOT.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le petit foot de Dounia</t>
+          <t>L'arrosoir qui goutte</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JEU.REG.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'arrosoir vert goutte encore. Victorina se passe le ballon avec maman. Elle vise le but. Elle reste dans l'espace montré.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dounia et maman arrivent au jardin. L'herbe sent l'été. Maman pose deux gourdes. Elle trace un petit rectangle. Voici l'espace montré. On reste dans l'espace montré. Au fond, maman pose deux paniers. C'est le but. Dounia touche le ballon du pied. Le ballon est souple. On va passer le ballon. Puis on vise le but. Dounia passe le ballon à maman. Maman le rend. Dounia pousse le ballon vers le but. Le ballon roule entre les paniers. Dounia lève les bras. On reste dans le rectangle. Dounia ramène le ballon. Elle passe encore. Elle vise encore le but. Les pieds restent dans l'espace montré par maman.</t>
+          <t>L'arrosoir vert penche encore. Une goutte tombe sur la terre. La terre la boit. Les tomates sentent le soleil. Un tuyau est enroulé. Il est tiède. Une feuille de basilic sent fort. Tu as senti ? Ça pique le nez. C'est le basilic. De la terre colle au bord de l'arrosoir. Elle est brune. Oui. Toute fine. Victorina touche une tomate. Elle est chaude. Le soleil l'a touchée. Tu as vu la goutte, Victorina ? Oui, maman. Elle est ronde. Une abeille va sur une fleur. Elle fait un petit zzz. Maman pose le sac. En ce moment, Victorina est au jardin. Maman pose deux gourdes. Elle trace un petit rectangle. Voici l'espace montré. On reste dans l'espace montré. Au fond, maman pose deux paniers. C'est le but. Victorina touche le ballon du pied. Le ballon est souple. Il est doux. On va passer le ballon. Puis on vise le but. Victorina passe le ballon à maman. Maman le rend. Bravo. Tu as passé. Victorina pousse le ballon vers le but. Le ballon roule entre les paniers. Victorina lève les bras. Dedans ! Bravo. Tu as visé le but. On reste dans le rectangle. Victorina ramène le ballon. Elle passe encore. Elle vise encore le but. Les pieds restent dans l'espace montré. L'arrosoir goutte encore. Ploc. L'abeille est partie. Un dernier passage ? Oui, maman. Victorina passe. Maman rend. Victorina pousse vers le but. Le ballon roule entre les paniers. Bravo. Tu as passé. Tu as visé le but. Dans l'espace montré.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1329,76 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Dounia et maman arrivent au jardin. L'herbe sent l'été. Maman pose deux gourdes. Elle trace un petit rectangle.
-maman|Voici l'espace montré. On reste dans l'espace montré. Au fond, maman pose deux paniers. C'est le but.
-narrateur|Dounia touche le ballon du pied. Le ballon est souple.
+          <t>narrateur|L'arrosoir vert penche encore.
+narrateur|Une goutte tombe sur la terre.
+narrateur|La terre la boit.
+narrateur|Les tomates sentent le soleil.
+narrateur|Un tuyau est enroulé.
+narrateur|Il est tiède.
+narrateur|Une feuille de basilic sent fort.
+maman|Tu as senti ?
+enfant-f|Ça pique le nez.
+maman|C'est le basilic.
+narrateur|De la terre colle au bord de l'arrosoir.
+enfant-f|Elle est brune.
+maman|Oui.
+maman|Toute fine.
+narrateur|Victorina touche une tomate.
+enfant-f|Elle est chaude.
+maman|Le soleil l'a touchée.
+maman|Tu as vu la goutte, Victorina ?
+enfant-f|Oui, maman.
+enfant-f|Elle est ronde.
+narrateur|Une abeille va sur une fleur.
+narrateur|Elle fait un petit zzz.
+narrateur|Maman pose le sac.
+narrateur|En ce moment, Victorina est au jardin.
+narrateur|Maman pose deux gourdes.
+narrateur|Elle trace un petit rectangle.
+maman|Voici l'espace montré.
+maman|On reste dans l'espace montré.
+narrateur|Au fond, maman pose deux paniers.
+narrateur|C'est le but.
+narrateur|Victorina touche le ballon du pied.
+narrateur|Le ballon est souple.
+enfant-f|Il est doux.
 maman|On va passer le ballon.
-narrateur|Puis on vise le but. Dounia passe le ballon à maman. Maman le rend. Dounia pousse le ballon vers le but. Le ballon roule entre les paniers. Dounia lève les bras.
+maman|Puis on vise le but.
+narrateur|Victorina passe le ballon à maman.
+narrateur|Maman le rend.
+maman|Bravo.
+maman|Tu as passé.
+narrateur|Victorina pousse le ballon vers le but.
+narrateur|Le ballon roule entre les paniers.
+narrateur|Victorina lève les bras.
+enfant-f|Dedans !
+maman|Bravo.
+maman|Tu as visé le but.
 maman|On reste dans le rectangle.
-narrateur|Dounia ramène le ballon. Elle passe encore. Elle vise encore le but. Les pieds restent dans l'espace montré par maman.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Victorina ramène le ballon.
+narrateur|Elle passe encore.
+narrateur|Elle vise encore le but.
+narrateur|Les pieds restent dans l'espace montré.
+narrateur|L'arrosoir goutte encore.
+narrateur|Ploc.
+enfant-f|L'abeille est partie.
+maman|Un dernier passage ?
+enfant-f|Oui, maman.
+narrateur|Victorina passe.
+narrateur|Maman rend.
+narrateur|Victorina pousse vers le but.
+narrateur|Le ballon roule entre les paniers.
+maman|Bravo.
+maman|Tu as passé.
+maman|Tu as visé le but.
+maman|Dans l'espace montré.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>goutte,ballon</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1423,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Dounia joue au foot. Que fait-elle ?</t>
+          <t>Victorina joue au foot. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1579,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Dounia joue au foot. Que fait-elle ?</t>
+          <t>narrateur|Victorina joue au foot.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1608,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dounia a passé le ballon. Elle a visé le but. Elle est restée dans l'espace montré par maman.</t>
+          <t>Victorina a passé le ballon. Elle a visé le but. Elle est restée dans l'espace montré par maman. Tu as passé. Bravo. Tu as visé le but. Dans l'espace montré.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1752,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Dounia a passé le ballon. Elle a visé le but. Elle est restée dans l'espace montré par maman.</t>
+          <t>narrateur|Victorina a passé le ballon.
+narrateur|Elle a visé le but.
+narrateur|Elle est restée dans l'espace montré par maman.
+maman|Tu as passé.
+maman|Bravo.
+maman|Tu as visé le but.
+enfant-f|Dans l'espace montré.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1786,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range les paniers. Dounia boit une gorgée. Elles marchent vers la maison.</t>
+          <t>Maman range les paniers. Victorina boit une gorgée. L'eau sent le jardin. L'arrosoir ne goutte plus. Tu as visé le but. Oui, maman. J'ai passé. Dans l'espace montré. Bravo. Tu as fait du bon travail. Elles marchent vers la maison. Les tomates restent au soleil. Le tuyau est encore enroulé. Le basilic sent encore. Ça pique le nez. Oui. Tu as passé. Tu as visé le but. Dans l'espace montré. C'est ça. Une goutte sèche sur la terre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,10 +1922,34 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range les paniers. Dounia boit une gorgée. Elles marchent vers la maison.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman range les paniers.
+narrateur|Victorina boit une gorgée.
+narrateur|L'eau sent le jardin.
+narrateur|L'arrosoir ne goutte plus.
+maman|Tu as visé le but.
+enfant-f|Oui, maman.
+enfant-f|J'ai passé.
+enfant-f|Dans l'espace montré.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Elles marchent vers la maison.
+narrateur|Les tomates restent au soleil.
+narrateur|Le tuyau est encore enroulé.
+narrateur|Le basilic sent encore.
+enfant-f|Ça pique le nez.
+maman|Oui.
+maman|Tu as passé.
+maman|Tu as visé le but.
+enfant-f|Dans l'espace montré.
+maman|C'est ça.
+narrateur|Une goutte sèche sur la terre.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>pas</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1866,7 +1974,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'arrosoir vert est droit maintenant. J'ai passé. J'ai visé le but. Bravo, Victorina. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2114,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'arrosoir vert est droit maintenant.
+enfant-f|J'ai passé.
+enfant-f|J'ai visé le but.
+maman|Bravo, Victorina.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2178,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.FOOT.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-03.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dounia et maman arrivent au jardin. L'herbe sent l'été. Maman pose deux gourdes. Elle trace un petit rectangle. Maman dit : voici l'espace montré. On reste dans l'espace montré. Au fond, maman pose deux paniers. C'est le &lt;emphasis level="moderate"&gt;but&lt;/emphasis&gt;. Dounia touche le ballon du pied. Le ballon est souple. Maman dit : on va passer le ballon. Puis on vise le but. Dounia passe le ballon à maman. Maman le rend. Dounia pousse le ballon vers le but. Le ballon roule entre les paniers. Dounia lève les bras. Maman dit : on reste dans le rectangle. Dounia ramène le ballon. Elle passe encore. Elle vise encore le but. Les pieds restent dans l'espace montré par maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'arrosoir vert penche encore. Une goutte tombe sur la terre. La terre la boit. Les tomates sentent le soleil. Un tuyau est enroulé. Il est tiède. Une feuille de basilic sent fort. Tu as senti ? Ça pique le nez. C'est le basilic. De la terre colle au bord de l'arrosoir. Elle est brune. Oui. Toute fine. Victorina touche une tomate. Elle est chaude. Le soleil l'a touchée. Tu as vu la goutte, Victorina ? Oui, maman. Elle est ronde. Une abeille va sur une fleur. Elle fait un petit zzz. Maman pose le sac. En ce moment, Victorina est au jardin. Maman pose deux gourdes. Elle trace un petit rectangle. Voici l'espace montré. On reste dans l'espace montré. Au fond, maman pose deux paniers. C'est le but. Victorina touche le ballon du pied. Le ballon est souple. Il est doux. On va passer le ballon. Puis on vise le but. Victorina passe le ballon à maman. Maman le rend. Bravo. Tu as passé. Victorina pousse le ballon vers le but. Le ballon roule entre les paniers. Victorina lève les bras. Dedans ! Bravo. Tu as visé le but. On reste dans le rectangle. Victorina ramène le ballon. Elle passe encore. Elle vise encore le but. Les pieds restent dans l'espace montré. L'arrosoir goutte encore. Ploc. L'abeille est partie. Un dernier passage ? Oui, maman. Victorina passe. Maman rend. Victorina pousse vers le but. Le ballon roule entre les paniers. Bravo. Tu as passé. Tu as visé le but. Dans l'espace montré.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Dounia joue au foot. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina joue au foot. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1583,7 +1583,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1613,7 +1612,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dounia a passé le ballon. Elle a visé le &lt;emphasis level="moderate"&gt;but&lt;/emphasis&gt;. Elle est restée dans l'espace montré par maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a passé le ballon. Elle a visé le but. Elle est restée dans l'espace montré par maman. Tu as passé. Bravo. Tu as visé le but. Dans l'espace montré.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1761,7 +1760,6 @@
 enfant-f|Dans l'espace montré.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1786,12 +1784,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range les paniers. Victorina boit une gorgée. L'eau sent le jardin. L'arrosoir ne goutte plus. Tu as visé le but. Oui, maman. J'ai passé. Dans l'espace montré. Bravo. Tu as fait du bon travail. Elles marchent vers la maison. Les tomates restent au soleil. Le tuyau est encore enroulé. Le basilic sent encore. Ça pique le nez. Oui. Tu as passé. Tu as visé le but. Dans l'espace montré. C'est ça. Une goutte sèche sur la terre.</t>
+          <t>Maman range les paniers. Victorina boit une gorgée. L'eau sent le jardin. L'arrosoir ne goutte plus. Tu as visé le but. Oui, maman. J'ai passé. Dans l'espace montré. Bravo. Elles marchent vers la maison. Les tomates restent au soleil. Le tuyau est encore enroulé. Le basilic sent encore. Ça pique le nez. Oui. Tu as passé. Tu as visé le but. Dans l'espace montré. C'est ça. Une goutte sèche sur la terre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range les paniers. Dounia boit une gorgée. Elles marchent vers la maison.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman range les paniers. Victorina boit une gorgée. L'eau sent le jardin. L'arrosoir ne goutte plus. Tu as visé le but. Oui, maman. J'ai passé. Dans l'espace montré. Bravo. Elles marchent vers la maison. Les tomates restent au soleil. Le tuyau est encore enroulé. Le basilic sent encore. Ça pique le nez. Oui. Tu as passé. Tu as visé le but. Dans l'espace montré. C'est ça. Une goutte sèche sur la terre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1931,7 +1929,6 @@
 enfant-f|J'ai passé.
 enfant-f|Dans l'espace montré.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 narrateur|Elles marchent vers la maison.
 narrateur|Les tomates restent au soleil.
 narrateur|Le tuyau est encore enroulé.
@@ -1974,12 +1971,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'arrosoir vert est droit maintenant. J'ai passé. J'ai visé le but. Bravo, Victorina. L'histoire est finie.</t>
+          <t>L'arrosoir vert est droit maintenant. J'ai passé. J'ai visé le but. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'arrosoir vert est droit maintenant. J'ai passé. J'ai visé le but. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2117,11 +2114,9 @@
           <t>narrateur|L'arrosoir vert est droit maintenant.
 enfant-f|J'ai passé.
 enfant-f|J'ai visé le but.
-maman|Bravo, Victorina.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo, Victorina.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2140,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2185,6 +2180,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.FOOT.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-03.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dounia, maman</t>
+          <t>Victorina, maman</t>
         </is>
       </c>
     </row>
